--- a/organization/VD_target_catalog.xlsx
+++ b/organization/VD_target_catalog.xlsx
@@ -785,9 +785,9 @@
           <t>Chassis, Suspension</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Steady-state handling + lap sim</t>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>run_wdist_targets (T-WDIST)</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -800,13 +800,21 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Provisional</t>
+        </is>
+      </c>
+      <c r="H6" s="25" t="inlineStr">
+        <is>
+          <t>44-47% front (prov.); current 40% = accel-aggressive</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED 2026-07-14 via run_wdist_targets (mid-tier sweep of mass_dist_f). KEY: lateral grip is FLAT vs weight split (~1% over 38-52% front, front-limited/stable throughout), so weight distribution is a TRACTION-vs-TRANSIENT-STABILITY call, not a grip one. Every steady-state metric favours rearward: launch traction +24% at 38% vs 50% front (RWD, rear axle carries drive load); braking mildly improves rearward (load shifts forward under braking); LLTD can balance the limit across the whole range (LLTD_neutral 0.47-0.58, all in authority). *** The steady-state models CANNOT locate the rearward limit - they favour rear monotonically. The real limit is TRANSIENT yaw stability (turn-in, trail-brake rotation, snap-oversteer) which is NOT modelled (roadmap #5 / track data). *** Target issued as 'rearmost that transient stability allows'; 44% floor is FSAE convention, PROVISIONAL. Current 40% front is accel-optimal but BELOW that floor: validate transient stability before committing this rearward. Principle: set weight distribution for traction/packaging (a one-time decision); trim handling balance with LLTD (a per-session knob) - do not chase steady-state balance with weight distribution.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="6" t="n">

--- a/organization/VD_target_catalog.xlsx
+++ b/organization/VD_target_catalog.xlsx
@@ -1545,9 +1545,9 @@
           <t>Suspension</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Kinematics + steering feel</t>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>aligning_moment.m (T-CAS transfer chart)</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1560,13 +1560,21 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="10" t="n"/>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Provisional</t>
+        </is>
+      </c>
+      <c r="H26" s="25" t="inlineStr">
+        <is>
+          <t>3-6 deg caster (10-21 mm mech trail) = 51-65 N*m/tire peak; PRACTICE window, not a computed optimum</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED 2026-07-15; REWORKED 2026-07-19 for rigor. VD delivers the TRANSFER, not a picked number: steering torque/tire = Fy(a)*(mechanical + pneumatic trail), evaluated over a caster grid from the 250 lbf measured bin (track-derated Fy). Pneumatic trail COLLAPSES toward the limit, so with 0 caster the torque keeps only 26% of its mid-corner peak at the grip limit (~11.6 deg) = NUMB; adding constant mechanical trail (caster) holds it up. TRANSFER (caster deg -&gt; mech trail mm -&gt; peak / limit torque N*m -&gt; limit%% of peak): 0-&gt;0-&gt;37/10-&gt;26; 3-&gt;10.5-&gt;51/28-&gt;55; 4-&gt;14-&gt;56/34-&gt;61; 5-&gt;17.5-&gt;60/40-&gt;67; 6-&gt;21-&gt;65/46-&gt;71; 8-&gt;28-&gt;74/59-&gt;79. RECOMMENDED START = 3-6 deg caster (10-21 mm mech trail, 51-65 N*m/tire) - CITED practice range (passenger/FSAE positive caster ~3-6 deg), and both trails stay below peak pneumatic trail (~41 mm) so mechanical trail complements rather than OVERPOWERS the tire self-centering (FSAE guidance; no power steering). REMOVED the earlier 60-75%% "feel-retention" auto-selector: that threshold was an engineering heuristic, not literature-validated, so it cannot set a target. Steering finalizes the value against its EFFORT BUDGET once the steering ratio (#52) exists. R_e=0.20 m for trail&lt;-&gt;caster (mech trail = R_e*tan(caster); ground-trail approx, scrub/kingpin offset deferred to #22). PROVISIONAL: front-outer load 303 lbf is mid-tier (+/-10-20% with roll-stiffness + aero).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="6" t="n">
@@ -2966,9 +2974,9 @@
           <t>Steering</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Kinematics + load</t>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>aligning_moment.m (T-MZ)</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2981,13 +2989,21 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="7" t="n"/>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>Provisional</t>
+        </is>
+      </c>
+      <c r="H65" s="25" t="inlineStr">
+        <is>
+          <t>Mz ~52-70 N*m/tire (track band), belt 77.5 N*m rack-sizing upper bound @303 lbf. Pneumatic trail = diagnostic curve only, not a target</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>DELIVERED 2026-07-15 via aligning_moment.m. Front-outer design load 303 lbf (axle_grip, low-speed limit ay 1.46g) = steering worst case. PEAK self-aligning torque/front tire: belt 77.5 N*m (rack-sizing upper bound), track band 52-70 N*m (mu_derate 0.67 grip-limited .. lambda_Ca 0.90 low-slip). TRAIL: no single trail number is delivered as a target - the caster work (#20) uses the FULL measured trail(alpha) curve. A single "initial trail" is 0/0 at alpha-&gt;0 (noisy) and any operating-band pick (1-3 deg ~40 mm) is reported only as a DIAGNOSTIC. Canonical way to get a real initial trail if ever needed: fit the Pacejka cosine-form trail Magic Formula t(a)=Dt*cos[...] and read Dt (peak), or brush model t0 ~ (1/3..1/2)*half-contact-length (needs contact geometry). Trail collapses to ~0 by the limit -&gt; at-limit torque is MECHANICAL trail (caster) only. SCALING (literature-checked): pneumatic-trail lambda_t=1.0 (Pacejka baseline; trail=aligning/cornering stiffness, both structural, ratio ~surface-invariant). EXTRAPOLATION: Mz(Fz) fit evaluated at 303 lbf is only +8% past the furthest MEASURED load (281 lbf) - short, smooth; or take peak measured Mz + margin and skip it. Donor borrowing NOT used (cross-tire Mz shape scatters ~8-10%). Load model is MID-TIER and will move +/-10-20% with real roll-stiffness distribution + aero balance -&gt; re-issue then. Rack force = torque / steering arm (steering subteam geometry).</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="9" t="n">
@@ -3272,17 +3288,17 @@
       </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>Needs re-run</t>
+          <t>Provisional</t>
         </is>
       </c>
       <c r="H74" s="31" t="inlineStr">
         <is>
-          <t>STALE - do not quote</t>
+          <t>Endurance 68.7 s / autocross 45.0 s (axle, load-sensitive lateral limit = new default). Point-mass model was ~4.4% optimistic (endurance 65.7 s).</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr">
         <is>
-          <t>*** MUST RE-RUN (run_lap_targets) *** TWO independent changes since this number was issued: (1) grip is now curve-based (mu_y -10%), and (2) the track digitizer's scale was WRONG - GRID_PX was hard-coded 11.6 px when the sheets measure 12.00 px, a 3.4% distance error. Endurance is now 964 m (was 999 m); autocross 674 m (was 675 m, but its geometry also changed). The old ~31 s figure is invalid on both counts. Digitizer scale is now AUTO-CALIBRATED from the sheet grid, so this class of error cannot recur.</t>
+          <t>UPGRADED 2026-07-19: lap sim lateral limit now routes through ay_limit.m (p.grip_model). Default "axle" = load-sensitive per-axle grip (accounts for grip LOST to lateral load transfer, ay_lim ~0.88-0.90*mu_y); "pointmass" reproduces the old constant-mu lap for comparison. Longitudinal edges (accel/brake) still point-mass - this step is lateral-only. Numbers Python-validated (axle ay 1.44-1.53g vs point-mass 1.61-1.74g); RUN lap_report / run_lap_targets in MATLAB to confirm and promote. lap_report prints both model times side by side.</t>
         </is>
       </c>
     </row>
